--- a/Encollect_Web_SCB_P1/Cypress/fixtures/AgentTemplate.xlsx
+++ b/Encollect_Web_SCB_P1/Cypress/fixtures/AgentTemplate.xlsx
@@ -404,61 +404,61 @@
         <v>123456</v>
       </c>
       <c r="B2" t="str">
-        <v>Bernhard</v>
+        <v>Hagenes</v>
       </c>
       <c r="C2" t="str">
-        <v>YMOPRW</v>
+        <v>UL25ME</v>
       </c>
       <c r="D2" t="str">
-        <v>Herta28@yahoo.com</v>
+        <v>Gerard.Nitzsche@gmail.com</v>
       </c>
       <c r="E2" t="str">
-        <v>86DtBuM8</v>
+        <v>wRagjZ3d</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-06-04</v>
+        <v>2025-05-05</v>
       </c>
       <c r="G2" t="str">
+        <v>2025-11-23</v>
+      </c>
+      <c r="H2" t="str">
+        <v>K7rUql0ibW</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Garden</v>
+      </c>
+      <c r="J2" t="str">
+        <v>International Metrics Administrator</v>
+      </c>
+      <c r="K2" t="str">
+        <v>2025-04-09</v>
+      </c>
+      <c r="L2" t="str">
+        <v>6984703443</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Casimer95@gmail.com</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Chloe</v>
+      </c>
+      <c r="O2" t="str">
+        <v>452 Lauriane Fords</v>
+      </c>
+      <c r="P2" t="str">
+        <v>66351</v>
+      </c>
+      <c r="Q2" t="str">
         <v>2025-10-13</v>
       </c>
-      <c r="H2" t="str">
-        <v>mHP0ERxOpQ</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Outdoors</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Product Identity Engineer</v>
-      </c>
-      <c r="K2" t="str">
-        <v>2025-05-16</v>
-      </c>
-      <c r="L2" t="str">
-        <v>6032843727</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Dandre77@hotmail.com</v>
-      </c>
-      <c r="N2" t="str">
-        <v>Kyleigh</v>
-      </c>
-      <c r="O2" t="str">
-        <v>9543 Grayce Tunnel</v>
-      </c>
-      <c r="P2" t="str">
-        <v>17570-3561</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>2025-11-18</v>
-      </c>
       <c r="R2" t="str">
-        <v>2025-03-11</v>
+        <v>2025-08-21</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-01-23</v>
+        <v>2026-12-23</v>
       </c>
       <c r="T2" t="str">
-        <v>Vivo adimpleo nostrum itaque comprehendo amaritudo coaegresco despecto.</v>
+        <v>Templum cedo corrigo.</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P1/Cypress/fixtures/AgentTemplate.xlsx
+++ b/Encollect_Web_SCB_P1/Cypress/fixtures/AgentTemplate.xlsx
@@ -404,61 +404,61 @@
         <v>123456</v>
       </c>
       <c r="B2" t="str">
-        <v>Hagenes</v>
+        <v>Treutel</v>
       </c>
       <c r="C2" t="str">
-        <v>UL25ME</v>
+        <v>HV3AQO</v>
       </c>
       <c r="D2" t="str">
-        <v>Gerard.Nitzsche@gmail.com</v>
+        <v>Destinee.Effertz@gmail.com</v>
       </c>
       <c r="E2" t="str">
-        <v>wRagjZ3d</v>
+        <v>fEEbn30n</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-05-05</v>
+        <v>2025-10-18</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-11-23</v>
+        <v>2025-12-19</v>
       </c>
       <c r="H2" t="str">
-        <v>K7rUql0ibW</v>
+        <v>4s0GQNM11H</v>
       </c>
       <c r="I2" t="str">
-        <v>Garden</v>
+        <v>Games</v>
       </c>
       <c r="J2" t="str">
-        <v>International Metrics Administrator</v>
+        <v>Customer Usability Representative</v>
       </c>
       <c r="K2" t="str">
-        <v>2025-04-09</v>
+        <v>2025-05-14</v>
       </c>
       <c r="L2" t="str">
-        <v>6984703443</v>
+        <v>0531805539</v>
       </c>
       <c r="M2" t="str">
-        <v>Casimer95@gmail.com</v>
+        <v>Russell.Cronin@gmail.com</v>
       </c>
       <c r="N2" t="str">
-        <v>Chloe</v>
+        <v>Vicky</v>
       </c>
       <c r="O2" t="str">
-        <v>452 Lauriane Fords</v>
+        <v>511 Kallie Club</v>
       </c>
       <c r="P2" t="str">
-        <v>66351</v>
+        <v>29742-2697</v>
       </c>
       <c r="Q2" t="str">
-        <v>2025-10-13</v>
+        <v>2025-09-06</v>
       </c>
       <c r="R2" t="str">
-        <v>2025-08-21</v>
+        <v>2025-05-09</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-12-23</v>
+        <v>2026-06-06</v>
       </c>
       <c r="T2" t="str">
-        <v>Templum cedo corrigo.</v>
+        <v>Spero contigo fuga vetus ullus advenio creator delectus curis.</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_SCB_P1/Cypress/fixtures/AgentTemplate.xlsx
+++ b/Encollect_Web_SCB_P1/Cypress/fixtures/AgentTemplate.xlsx
@@ -404,61 +404,61 @@
         <v>123456</v>
       </c>
       <c r="B2" t="str">
-        <v>Treutel</v>
+        <v>Robel</v>
       </c>
       <c r="C2" t="str">
-        <v>HV3AQO</v>
+        <v>RHQHSP</v>
       </c>
       <c r="D2" t="str">
-        <v>Destinee.Effertz@gmail.com</v>
+        <v>Eduardo22@yahoo.com</v>
       </c>
       <c r="E2" t="str">
-        <v>fEEbn30n</v>
+        <v>8YcQIaPf</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-10-18</v>
+        <v>2026-04-28</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-12-19</v>
+        <v>2026-02-24</v>
       </c>
       <c r="H2" t="str">
-        <v>4s0GQNM11H</v>
+        <v>0NZ9RE87Ox</v>
       </c>
       <c r="I2" t="str">
         <v>Games</v>
       </c>
       <c r="J2" t="str">
-        <v>Customer Usability Representative</v>
+        <v>Legacy Group Agent</v>
       </c>
       <c r="K2" t="str">
-        <v>2025-05-14</v>
+        <v>2025-08-29</v>
       </c>
       <c r="L2" t="str">
-        <v>0531805539</v>
+        <v>0396733255</v>
       </c>
       <c r="M2" t="str">
-        <v>Russell.Cronin@gmail.com</v>
+        <v>Terence48@hotmail.com</v>
       </c>
       <c r="N2" t="str">
-        <v>Vicky</v>
+        <v>Yasmin</v>
       </c>
       <c r="O2" t="str">
-        <v>511 Kallie Club</v>
+        <v>797 Dexter Dale</v>
       </c>
       <c r="P2" t="str">
-        <v>29742-2697</v>
+        <v>04567</v>
       </c>
       <c r="Q2" t="str">
-        <v>2025-09-06</v>
+        <v>2026-01-20</v>
       </c>
       <c r="R2" t="str">
-        <v>2025-05-09</v>
+        <v>2025-06-27</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-07-17</v>
       </c>
       <c r="T2" t="str">
-        <v>Spero contigo fuga vetus ullus advenio creator delectus curis.</v>
+        <v>Candidus curo fugit.</v>
       </c>
     </row>
   </sheetData>
